--- a/output/graficos_dimensiones/comunal_s_isapre_a_2024_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_s_isapre_a_2024_nuble.xlsx
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 20:06</t>
+    <t xml:space="preserve">2026-09-09 22:59</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_s_isapre_a_2024_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_s_isapre_a_2024_nuble.xlsx
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 22:59</t>
+    <t xml:space="preserve">2026-09-18 10:24</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_s_isapre_a_2024_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_s_isapre_a_2024_nuble.xlsx
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 10:24</t>
+    <t xml:space="preserve">2026-09-23 12:26</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_s_isapre_a_2024_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_s_isapre_a_2024_nuble.xlsx
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 12:26</t>
+    <t xml:space="preserve">2026-10-02 14:04</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_s_isapre_a_2024_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_s_isapre_a_2024_nuble.xlsx
@@ -42,7 +42,7 @@
     <t xml:space="preserve">Yungay</t>
   </si>
   <si>
-    <t xml:space="preserve">Ranquil</t>
+    <t xml:space="preserve">Ránquil</t>
   </si>
   <si>
     <t xml:space="preserve">Chillán Viejo</t>
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 14:04</t>
+    <t xml:space="preserve">2026-10-04 08:46</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_s_isapre_a_2024_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_s_isapre_a_2024_nuble.xlsx
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 08:46</t>
+    <t xml:space="preserve">2026-10-05 09:55</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
